--- a/TIMES-NZ/v303/SuppXLS/Scen_Base_Constraints.xlsx
+++ b/TIMES-NZ/v303/SuppXLS/Scen_Base_Constraints.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VehicleUtilisation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GasNetwork" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,9 +518,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v/>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>LO</t>
@@ -547,36 +545,15 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v/>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>T_P_CICEPET_LOW,T_P_CICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v/>
-      </c>
-      <c r="D6" t="n">
-        <v/>
-      </c>
-      <c r="E6" t="n">
-        <v/>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G6" t="n">
-        <v/>
-      </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -595,9 +572,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v/>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>LO</t>
@@ -625,36 +599,15 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v/>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>T_P_CICEPET_MED,T_P_CICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v/>
-      </c>
-      <c r="D8" t="n">
-        <v/>
-      </c>
-      <c r="E8" t="n">
-        <v/>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G8" t="n">
-        <v/>
-      </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="I8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -673,9 +626,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v/>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>LO</t>
@@ -703,36 +653,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v/>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>T_P_CICEPET_LOW,T_P_CICEPET_MED</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v/>
-      </c>
-      <c r="D10" t="n">
-        <v/>
-      </c>
-      <c r="E10" t="n">
-        <v/>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G10" t="n">
-        <v/>
-      </c>
-      <c r="H10" t="n">
-        <v/>
-      </c>
-      <c r="I10" t="n">
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -751,9 +680,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v/>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>LO</t>
@@ -781,36 +707,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v/>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>T_P_CICEDSL_LOW,T_P_CICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v/>
-      </c>
-      <c r="D12" t="n">
-        <v/>
-      </c>
-      <c r="E12" t="n">
-        <v/>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G12" t="n">
-        <v/>
-      </c>
-      <c r="H12" t="n">
-        <v/>
-      </c>
-      <c r="I12" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -829,9 +734,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v/>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>LO</t>
@@ -859,36 +761,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v/>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>T_P_CICEDSL_MED,T_P_CICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v/>
-      </c>
-      <c r="D14" t="n">
-        <v/>
-      </c>
-      <c r="E14" t="n">
-        <v/>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G14" t="n">
-        <v/>
-      </c>
-      <c r="H14" t="n">
-        <v/>
-      </c>
-      <c r="I14" t="n">
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -907,9 +788,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v/>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>LO</t>
@@ -937,36 +815,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v/>
-      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>T_P_CICEDSL_LOW,T_P_CICEDSL_MED</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v/>
-      </c>
-      <c r="D16" t="n">
-        <v/>
-      </c>
-      <c r="E16" t="n">
-        <v/>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G16" t="n">
-        <v/>
-      </c>
-      <c r="H16" t="n">
-        <v/>
-      </c>
-      <c r="I16" t="n">
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -985,9 +842,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v/>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1015,36 +869,15 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v/>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>T_P_CBEVNEW_LOW,T_P_CBEVNEW_HIGH</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v/>
-      </c>
-      <c r="D18" t="n">
-        <v/>
-      </c>
-      <c r="E18" t="n">
-        <v/>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G18" t="n">
-        <v/>
-      </c>
-      <c r="H18" t="n">
-        <v/>
-      </c>
-      <c r="I18" t="n">
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -1063,9 +896,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v/>
-      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1093,36 +923,15 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v/>
-      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>T_P_CBEVNEW_MED,T_P_CBEVNEW_HIGH</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v/>
-      </c>
-      <c r="D20" t="n">
-        <v/>
-      </c>
-      <c r="E20" t="n">
-        <v/>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G20" t="n">
-        <v/>
-      </c>
-      <c r="H20" t="n">
-        <v/>
-      </c>
-      <c r="I20" t="n">
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -1141,9 +950,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v/>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1171,36 +977,15 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v/>
-      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>T_P_CBEVNEW_LOW,T_P_CBEVNEW_MED</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v/>
-      </c>
-      <c r="D22" t="n">
-        <v/>
-      </c>
-      <c r="E22" t="n">
-        <v/>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G22" t="n">
-        <v/>
-      </c>
-      <c r="H22" t="n">
-        <v/>
-      </c>
-      <c r="I22" t="n">
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -1219,9 +1004,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v/>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1249,36 +1031,15 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v/>
-      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>T_P_CBEVUSD_LOW,T_P_CBEVUSD_HIGH</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v/>
-      </c>
-      <c r="D24" t="n">
-        <v/>
-      </c>
-      <c r="E24" t="n">
-        <v/>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G24" t="n">
-        <v/>
-      </c>
-      <c r="H24" t="n">
-        <v/>
-      </c>
-      <c r="I24" t="n">
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -1297,9 +1058,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v/>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1327,36 +1085,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v/>
-      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>T_P_CBEVUSD_MED,T_P_CBEVUSD_HIGH</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v/>
-      </c>
-      <c r="D26" t="n">
-        <v/>
-      </c>
-      <c r="E26" t="n">
-        <v/>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G26" t="n">
-        <v/>
-      </c>
-      <c r="H26" t="n">
-        <v/>
-      </c>
-      <c r="I26" t="n">
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -1375,9 +1112,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v/>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1405,36 +1139,15 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v/>
-      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>T_P_CBEVUSD_LOW,T_P_CBEVUSD_MED</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v/>
-      </c>
-      <c r="D28" t="n">
-        <v/>
-      </c>
-      <c r="E28" t="n">
-        <v/>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G28" t="n">
-        <v/>
-      </c>
-      <c r="H28" t="n">
-        <v/>
-      </c>
-      <c r="I28" t="n">
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -1453,9 +1166,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v/>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1483,36 +1193,15 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v/>
-      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>T_P_CBEVELC_LOW,T_P_CBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v/>
-      </c>
-      <c r="D30" t="n">
-        <v/>
-      </c>
-      <c r="E30" t="n">
-        <v/>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G30" t="n">
-        <v/>
-      </c>
-      <c r="H30" t="n">
-        <v/>
-      </c>
-      <c r="I30" t="n">
-        <v/>
       </c>
     </row>
     <row r="31">
@@ -1531,9 +1220,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v/>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1561,36 +1247,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v/>
-      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>T_P_CBEVELC_MED,T_P_CBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v/>
-      </c>
-      <c r="D32" t="n">
-        <v/>
-      </c>
-      <c r="E32" t="n">
-        <v/>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G32" t="n">
-        <v/>
-      </c>
-      <c r="H32" t="n">
-        <v/>
-      </c>
-      <c r="I32" t="n">
-        <v/>
       </c>
     </row>
     <row r="33">
@@ -1609,9 +1274,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v/>
-      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1639,36 +1301,15 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v/>
-      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>T_P_CBEVELC_LOW,T_P_CBEVELC_MED</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v/>
-      </c>
-      <c r="D34" t="n">
-        <v/>
-      </c>
-      <c r="E34" t="n">
-        <v/>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G34" t="n">
-        <v/>
-      </c>
-      <c r="H34" t="n">
-        <v/>
-      </c>
-      <c r="I34" t="n">
-        <v/>
       </c>
     </row>
     <row r="35">
@@ -1687,9 +1328,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v/>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1717,36 +1355,15 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v/>
-      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>T_P_CICELPG_LOW,T_P_CICELPG_HIGH</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v/>
-      </c>
-      <c r="D36" t="n">
-        <v/>
-      </c>
-      <c r="E36" t="n">
-        <v/>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G36" t="n">
-        <v/>
-      </c>
-      <c r="H36" t="n">
-        <v/>
-      </c>
-      <c r="I36" t="n">
-        <v/>
       </c>
     </row>
     <row r="37">
@@ -1765,9 +1382,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v/>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1795,36 +1409,15 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v/>
-      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>T_P_CICELPG_MED,T_P_CICELPG_HIGH</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v/>
-      </c>
-      <c r="D38" t="n">
-        <v/>
-      </c>
-      <c r="E38" t="n">
-        <v/>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G38" t="n">
-        <v/>
-      </c>
-      <c r="H38" t="n">
-        <v/>
-      </c>
-      <c r="I38" t="n">
-        <v/>
       </c>
     </row>
     <row r="39">
@@ -1843,9 +1436,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v/>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1873,36 +1463,15 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v/>
-      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>T_P_CICELPG_LOW,T_P_CICELPG_MED</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v/>
-      </c>
-      <c r="D40" t="n">
-        <v/>
-      </c>
-      <c r="E40" t="n">
-        <v/>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G40" t="n">
-        <v/>
-      </c>
-      <c r="H40" t="n">
-        <v/>
-      </c>
-      <c r="I40" t="n">
-        <v/>
       </c>
     </row>
     <row r="41">
@@ -1921,9 +1490,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v/>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>LO</t>
@@ -1951,36 +1517,15 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v/>
-      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>T_P_CHYBPET_LOW,T_P_CHYBPET_HIGH</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v/>
-      </c>
-      <c r="D42" t="n">
-        <v/>
-      </c>
-      <c r="E42" t="n">
-        <v/>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G42" t="n">
-        <v/>
-      </c>
-      <c r="H42" t="n">
-        <v/>
-      </c>
-      <c r="I42" t="n">
-        <v/>
       </c>
     </row>
     <row r="43">
@@ -1999,9 +1544,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v/>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2029,36 +1571,15 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v/>
-      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>T_P_CHYBPET_MED,T_P_CHYBPET_HIGH</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v/>
-      </c>
-      <c r="D44" t="n">
-        <v/>
-      </c>
-      <c r="E44" t="n">
-        <v/>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G44" t="n">
-        <v/>
-      </c>
-      <c r="H44" t="n">
-        <v/>
-      </c>
-      <c r="I44" t="n">
-        <v/>
       </c>
     </row>
     <row r="45">
@@ -2077,9 +1598,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v/>
-      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2107,36 +1625,15 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v/>
-      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>T_P_CHYBPET_LOW,T_P_CHYBPET_MED</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v/>
-      </c>
-      <c r="D46" t="n">
-        <v/>
-      </c>
-      <c r="E46" t="n">
-        <v/>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G46" t="n">
-        <v/>
-      </c>
-      <c r="H46" t="n">
-        <v/>
-      </c>
-      <c r="I46" t="n">
-        <v/>
       </c>
     </row>
     <row r="47">
@@ -2155,9 +1652,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v/>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2185,36 +1679,15 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v/>
-      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>T_P_CPHEVPET_LOW,T_P_CPHEVPET_HIGH</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v/>
-      </c>
-      <c r="D48" t="n">
-        <v/>
-      </c>
-      <c r="E48" t="n">
-        <v/>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G48" t="n">
-        <v/>
-      </c>
-      <c r="H48" t="n">
-        <v/>
-      </c>
-      <c r="I48" t="n">
-        <v/>
       </c>
     </row>
     <row r="49">
@@ -2233,9 +1706,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v/>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2263,36 +1733,15 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v/>
-      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>T_P_CPHEVPET_MED,T_P_CPHEVPET_HIGH</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v/>
-      </c>
-      <c r="D50" t="n">
-        <v/>
-      </c>
-      <c r="E50" t="n">
-        <v/>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G50" t="n">
-        <v/>
-      </c>
-      <c r="H50" t="n">
-        <v/>
-      </c>
-      <c r="I50" t="n">
-        <v/>
       </c>
     </row>
     <row r="51">
@@ -2311,9 +1760,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v/>
-      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2341,36 +1787,15 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v/>
-      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>T_P_CPHEVPET_LOW,T_P_CPHEVPET_MED</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v/>
-      </c>
-      <c r="D52" t="n">
-        <v/>
-      </c>
-      <c r="E52" t="n">
-        <v/>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G52" t="n">
-        <v/>
-      </c>
-      <c r="H52" t="n">
-        <v/>
-      </c>
-      <c r="I52" t="n">
-        <v/>
       </c>
     </row>
     <row r="53">
@@ -2389,9 +1814,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v/>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2419,36 +1841,15 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v/>
-      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>T_P_CPHEVBEV_LOW,T_P_CPHEVBEV_HIGH</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v/>
-      </c>
-      <c r="D54" t="n">
-        <v/>
-      </c>
-      <c r="E54" t="n">
-        <v/>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G54" t="n">
-        <v/>
-      </c>
-      <c r="H54" t="n">
-        <v/>
-      </c>
-      <c r="I54" t="n">
-        <v/>
       </c>
     </row>
     <row r="55">
@@ -2467,9 +1868,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v/>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2497,36 +1895,15 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v/>
-      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>T_P_CPHEVBEV_MED,T_P_CPHEVBEV_HIGH</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v/>
-      </c>
-      <c r="D56" t="n">
-        <v/>
-      </c>
-      <c r="E56" t="n">
-        <v/>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G56" t="n">
-        <v/>
-      </c>
-      <c r="H56" t="n">
-        <v/>
-      </c>
-      <c r="I56" t="n">
-        <v/>
       </c>
     </row>
     <row r="57">
@@ -2545,9 +1922,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v/>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2575,36 +1949,15 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v/>
-      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>T_P_CPHEVBEV_LOW,T_P_CPHEVBEV_MED</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v/>
-      </c>
-      <c r="D58" t="n">
-        <v/>
-      </c>
-      <c r="E58" t="n">
-        <v/>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G58" t="n">
-        <v/>
-      </c>
-      <c r="H58" t="n">
-        <v/>
-      </c>
-      <c r="I58" t="n">
-        <v/>
       </c>
     </row>
     <row r="59">
@@ -2623,9 +1976,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v/>
-      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2653,36 +2003,15 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v/>
-      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>T_P_CFCH2R_LOW,T_P_CFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v/>
-      </c>
-      <c r="D60" t="n">
-        <v/>
-      </c>
-      <c r="E60" t="n">
-        <v/>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G60" t="n">
-        <v/>
-      </c>
-      <c r="H60" t="n">
-        <v/>
-      </c>
-      <c r="I60" t="n">
-        <v/>
       </c>
     </row>
     <row r="61">
@@ -2701,9 +2030,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v/>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2731,36 +2057,15 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v/>
-      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>T_P_CFCH2R_MED,T_P_CFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v/>
-      </c>
-      <c r="D62" t="n">
-        <v/>
-      </c>
-      <c r="E62" t="n">
-        <v/>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G62" t="n">
-        <v/>
-      </c>
-      <c r="H62" t="n">
-        <v/>
-      </c>
-      <c r="I62" t="n">
-        <v/>
       </c>
     </row>
     <row r="63">
@@ -2779,9 +2084,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v/>
-      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2809,36 +2111,15 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v/>
-      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>T_P_CFCH2R_LOW,T_P_CFCH2R_MED</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v/>
-      </c>
-      <c r="D64" t="n">
-        <v/>
-      </c>
-      <c r="E64" t="n">
-        <v/>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G64" t="n">
-        <v/>
-      </c>
-      <c r="H64" t="n">
-        <v/>
-      </c>
-      <c r="I64" t="n">
-        <v/>
       </c>
     </row>
     <row r="65">
@@ -2857,9 +2138,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v/>
-      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2887,36 +2165,15 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v/>
-      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>T_P_CPHEVDSL_LOW,T_P_CPHEVDSL_HIGH</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v/>
-      </c>
-      <c r="D66" t="n">
-        <v/>
-      </c>
-      <c r="E66" t="n">
-        <v/>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G66" t="n">
-        <v/>
-      </c>
-      <c r="H66" t="n">
-        <v/>
-      </c>
-      <c r="I66" t="n">
-        <v/>
       </c>
     </row>
     <row r="67">
@@ -2935,9 +2192,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v/>
-      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>LO</t>
@@ -2965,36 +2219,15 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v/>
-      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>T_P_CPHEVDSL_MED,T_P_CPHEVDSL_HIGH</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v/>
-      </c>
-      <c r="D68" t="n">
-        <v/>
-      </c>
-      <c r="E68" t="n">
-        <v/>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G68" t="n">
-        <v/>
-      </c>
-      <c r="H68" t="n">
-        <v/>
-      </c>
-      <c r="I68" t="n">
-        <v/>
       </c>
     </row>
     <row r="69">
@@ -3013,9 +2246,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v/>
-      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3043,36 +2273,15 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v/>
-      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>T_P_CPHEVDSL_LOW,T_P_CPHEVDSL_MED</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v/>
-      </c>
-      <c r="D70" t="n">
-        <v/>
-      </c>
-      <c r="E70" t="n">
-        <v/>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G70" t="n">
-        <v/>
-      </c>
-      <c r="H70" t="n">
-        <v/>
-      </c>
-      <c r="I70" t="n">
-        <v/>
       </c>
     </row>
     <row r="71">
@@ -3091,9 +2300,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v/>
-      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3121,36 +2327,15 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v/>
-      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>T_C_CICEPET_LOW,T_C_CICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v/>
-      </c>
-      <c r="D72" t="n">
-        <v/>
-      </c>
-      <c r="E72" t="n">
-        <v/>
-      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G72" t="n">
-        <v/>
-      </c>
-      <c r="H72" t="n">
-        <v/>
-      </c>
-      <c r="I72" t="n">
-        <v/>
       </c>
     </row>
     <row r="73">
@@ -3169,9 +2354,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v/>
-      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3199,36 +2381,15 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v/>
-      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>T_C_CICEPET_MED,T_C_CICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v/>
-      </c>
-      <c r="D74" t="n">
-        <v/>
-      </c>
-      <c r="E74" t="n">
-        <v/>
-      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G74" t="n">
-        <v/>
-      </c>
-      <c r="H74" t="n">
-        <v/>
-      </c>
-      <c r="I74" t="n">
-        <v/>
       </c>
     </row>
     <row r="75">
@@ -3247,9 +2408,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v/>
-      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3277,36 +2435,15 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v/>
-      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>T_C_CICEPET_LOW,T_C_CICEPET_MED</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v/>
-      </c>
-      <c r="D76" t="n">
-        <v/>
-      </c>
-      <c r="E76" t="n">
-        <v/>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G76" t="n">
-        <v/>
-      </c>
-      <c r="H76" t="n">
-        <v/>
-      </c>
-      <c r="I76" t="n">
-        <v/>
       </c>
     </row>
     <row r="77">
@@ -3325,9 +2462,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v/>
-      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3355,36 +2489,15 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v/>
-      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>T_C_CICEDSL_LOW,T_C_CICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v/>
-      </c>
-      <c r="D78" t="n">
-        <v/>
-      </c>
-      <c r="E78" t="n">
-        <v/>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G78" t="n">
-        <v/>
-      </c>
-      <c r="H78" t="n">
-        <v/>
-      </c>
-      <c r="I78" t="n">
-        <v/>
       </c>
     </row>
     <row r="79">
@@ -3403,9 +2516,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v/>
-      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3433,36 +2543,15 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v/>
-      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>T_C_CICEDSL_MED,T_C_CICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v/>
-      </c>
-      <c r="D80" t="n">
-        <v/>
-      </c>
-      <c r="E80" t="n">
-        <v/>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G80" t="n">
-        <v/>
-      </c>
-      <c r="H80" t="n">
-        <v/>
-      </c>
-      <c r="I80" t="n">
-        <v/>
       </c>
     </row>
     <row r="81">
@@ -3481,9 +2570,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v/>
-      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3511,36 +2597,15 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v/>
-      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>T_C_CICEDSL_LOW,T_C_CICEDSL_MED</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v/>
-      </c>
-      <c r="D82" t="n">
-        <v/>
-      </c>
-      <c r="E82" t="n">
-        <v/>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G82" t="n">
-        <v/>
-      </c>
-      <c r="H82" t="n">
-        <v/>
-      </c>
-      <c r="I82" t="n">
-        <v/>
       </c>
     </row>
     <row r="83">
@@ -3559,9 +2624,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v/>
-      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3589,36 +2651,15 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v/>
-      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>T_C_CBEVNEW_LOW,T_C_CBEVNEW_HIGH</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v/>
-      </c>
-      <c r="D84" t="n">
-        <v/>
-      </c>
-      <c r="E84" t="n">
-        <v/>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G84" t="n">
-        <v/>
-      </c>
-      <c r="H84" t="n">
-        <v/>
-      </c>
-      <c r="I84" t="n">
-        <v/>
       </c>
     </row>
     <row r="85">
@@ -3637,9 +2678,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v/>
-      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3667,36 +2705,15 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v/>
-      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>T_C_CBEVNEW_MED,T_C_CBEVNEW_HIGH</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v/>
-      </c>
-      <c r="D86" t="n">
-        <v/>
-      </c>
-      <c r="E86" t="n">
-        <v/>
-      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G86" t="n">
-        <v/>
-      </c>
-      <c r="H86" t="n">
-        <v/>
-      </c>
-      <c r="I86" t="n">
-        <v/>
       </c>
     </row>
     <row r="87">
@@ -3715,9 +2732,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v/>
-      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3745,36 +2759,15 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v/>
-      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>T_C_CBEVNEW_LOW,T_C_CBEVNEW_MED</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v/>
-      </c>
-      <c r="D88" t="n">
-        <v/>
-      </c>
-      <c r="E88" t="n">
-        <v/>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G88" t="n">
-        <v/>
-      </c>
-      <c r="H88" t="n">
-        <v/>
-      </c>
-      <c r="I88" t="n">
-        <v/>
       </c>
     </row>
     <row r="89">
@@ -3793,9 +2786,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v/>
-      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3823,36 +2813,15 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v/>
-      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>T_C_CBEVELC_LOW,T_C_CBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v/>
-      </c>
-      <c r="D90" t="n">
-        <v/>
-      </c>
-      <c r="E90" t="n">
-        <v/>
-      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G90" t="n">
-        <v/>
-      </c>
-      <c r="H90" t="n">
-        <v/>
-      </c>
-      <c r="I90" t="n">
-        <v/>
       </c>
     </row>
     <row r="91">
@@ -3871,9 +2840,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v/>
-      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3901,36 +2867,15 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
-        <v/>
-      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>T_C_CBEVELC_MED,T_C_CBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v/>
-      </c>
-      <c r="D92" t="n">
-        <v/>
-      </c>
-      <c r="E92" t="n">
-        <v/>
-      </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G92" t="n">
-        <v/>
-      </c>
-      <c r="H92" t="n">
-        <v/>
-      </c>
-      <c r="I92" t="n">
-        <v/>
       </c>
     </row>
     <row r="93">
@@ -3949,9 +2894,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v/>
-      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>LO</t>
@@ -3979,36 +2921,15 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v/>
-      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>T_C_CBEVELC_LOW,T_C_CBEVELC_MED</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v/>
-      </c>
-      <c r="D94" t="n">
-        <v/>
-      </c>
-      <c r="E94" t="n">
-        <v/>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G94" t="n">
-        <v/>
-      </c>
-      <c r="H94" t="n">
-        <v/>
-      </c>
-      <c r="I94" t="n">
-        <v/>
       </c>
     </row>
     <row r="95">
@@ -4027,9 +2948,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v/>
-      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4057,36 +2975,15 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v/>
-      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>T_C_CICELPG_LOW,T_C_CICELPG_HIGH</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v/>
-      </c>
-      <c r="D96" t="n">
-        <v/>
-      </c>
-      <c r="E96" t="n">
-        <v/>
-      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G96" t="n">
-        <v/>
-      </c>
-      <c r="H96" t="n">
-        <v/>
-      </c>
-      <c r="I96" t="n">
-        <v/>
       </c>
     </row>
     <row r="97">
@@ -4105,9 +3002,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v/>
-      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4135,36 +3029,15 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
-        <v/>
-      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>T_C_CICELPG_MED,T_C_CICELPG_HIGH</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v/>
-      </c>
-      <c r="D98" t="n">
-        <v/>
-      </c>
-      <c r="E98" t="n">
-        <v/>
-      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G98" t="n">
-        <v/>
-      </c>
-      <c r="H98" t="n">
-        <v/>
-      </c>
-      <c r="I98" t="n">
-        <v/>
       </c>
     </row>
     <row r="99">
@@ -4183,9 +3056,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v/>
-      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4213,36 +3083,15 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
-        <v/>
-      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>T_C_CICELPG_LOW,T_C_CICELPG_MED</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v/>
-      </c>
-      <c r="D100" t="n">
-        <v/>
-      </c>
-      <c r="E100" t="n">
-        <v/>
-      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G100" t="n">
-        <v/>
-      </c>
-      <c r="H100" t="n">
-        <v/>
-      </c>
-      <c r="I100" t="n">
-        <v/>
       </c>
     </row>
     <row r="101">
@@ -4261,9 +3110,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v/>
-      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4291,36 +3137,15 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
-        <v/>
-      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>T_C_CFCH2R_LOW,T_C_CFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v/>
-      </c>
-      <c r="D102" t="n">
-        <v/>
-      </c>
-      <c r="E102" t="n">
-        <v/>
-      </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G102" t="n">
-        <v/>
-      </c>
-      <c r="H102" t="n">
-        <v/>
-      </c>
-      <c r="I102" t="n">
-        <v/>
       </c>
     </row>
     <row r="103">
@@ -4339,9 +3164,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v/>
-      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4369,36 +3191,15 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
-        <v/>
-      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>T_C_CFCH2R_MED,T_C_CFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v/>
-      </c>
-      <c r="D104" t="n">
-        <v/>
-      </c>
-      <c r="E104" t="n">
-        <v/>
-      </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G104" t="n">
-        <v/>
-      </c>
-      <c r="H104" t="n">
-        <v/>
-      </c>
-      <c r="I104" t="n">
-        <v/>
       </c>
     </row>
     <row r="105">
@@ -4417,9 +3218,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v/>
-      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4447,36 +3245,15 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
-        <v/>
-      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>T_C_CFCH2R_LOW,T_C_CFCH2R_MED</t>
         </is>
       </c>
-      <c r="C106" t="n">
-        <v/>
-      </c>
-      <c r="D106" t="n">
-        <v/>
-      </c>
-      <c r="E106" t="n">
-        <v/>
-      </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G106" t="n">
-        <v/>
-      </c>
-      <c r="H106" t="n">
-        <v/>
-      </c>
-      <c r="I106" t="n">
-        <v/>
       </c>
     </row>
     <row r="107">
@@ -4495,9 +3272,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v/>
-      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4525,36 +3299,15 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
-        <v/>
-      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>T_C_CPHEVDSL_LOW,T_C_CPHEVDSL_HIGH</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v/>
-      </c>
-      <c r="D108" t="n">
-        <v/>
-      </c>
-      <c r="E108" t="n">
-        <v/>
-      </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G108" t="n">
-        <v/>
-      </c>
-      <c r="H108" t="n">
-        <v/>
-      </c>
-      <c r="I108" t="n">
-        <v/>
       </c>
     </row>
     <row r="109">
@@ -4573,9 +3326,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v/>
-      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4603,36 +3353,15 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
-        <v/>
-      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>T_C_CPHEVDSL_MED,T_C_CPHEVDSL_HIGH</t>
         </is>
       </c>
-      <c r="C110" t="n">
-        <v/>
-      </c>
-      <c r="D110" t="n">
-        <v/>
-      </c>
-      <c r="E110" t="n">
-        <v/>
-      </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G110" t="n">
-        <v/>
-      </c>
-      <c r="H110" t="n">
-        <v/>
-      </c>
-      <c r="I110" t="n">
-        <v/>
       </c>
     </row>
     <row r="111">
@@ -4651,9 +3380,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v/>
-      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4681,36 +3407,15 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
-        <v/>
-      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>T_C_CPHEVDSL_LOW,T_C_CPHEVDSL_MED</t>
         </is>
       </c>
-      <c r="C112" t="n">
-        <v/>
-      </c>
-      <c r="D112" t="n">
-        <v/>
-      </c>
-      <c r="E112" t="n">
-        <v/>
-      </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G112" t="n">
-        <v/>
-      </c>
-      <c r="H112" t="n">
-        <v/>
-      </c>
-      <c r="I112" t="n">
-        <v/>
       </c>
     </row>
     <row r="113">
@@ -4729,9 +3434,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D113" t="n">
-        <v/>
-      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4759,36 +3461,15 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
-        <v/>
-      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>T_P_MICEPET_LOW,T_P_MICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C114" t="n">
-        <v/>
-      </c>
-      <c r="D114" t="n">
-        <v/>
-      </c>
-      <c r="E114" t="n">
-        <v/>
-      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G114" t="n">
-        <v/>
-      </c>
-      <c r="H114" t="n">
-        <v/>
-      </c>
-      <c r="I114" t="n">
-        <v/>
       </c>
     </row>
     <row r="115">
@@ -4807,9 +3488,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D115" t="n">
-        <v/>
-      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4837,36 +3515,15 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
-        <v/>
-      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>T_P_MICEPET_MED,T_P_MICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C116" t="n">
-        <v/>
-      </c>
-      <c r="D116" t="n">
-        <v/>
-      </c>
-      <c r="E116" t="n">
-        <v/>
-      </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G116" t="n">
-        <v/>
-      </c>
-      <c r="H116" t="n">
-        <v/>
-      </c>
-      <c r="I116" t="n">
-        <v/>
       </c>
     </row>
     <row r="117">
@@ -4885,9 +3542,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D117" t="n">
-        <v/>
-      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4915,36 +3569,15 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
-        <v/>
-      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>T_P_MICEPET_LOW,T_P_MICEPET_MED</t>
         </is>
       </c>
-      <c r="C118" t="n">
-        <v/>
-      </c>
-      <c r="D118" t="n">
-        <v/>
-      </c>
-      <c r="E118" t="n">
-        <v/>
-      </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G118" t="n">
-        <v/>
-      </c>
-      <c r="H118" t="n">
-        <v/>
-      </c>
-      <c r="I118" t="n">
-        <v/>
       </c>
     </row>
     <row r="119">
@@ -4963,9 +3596,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v/>
-      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>LO</t>
@@ -4993,36 +3623,15 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
-        <v/>
-      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>T_P_MBEVELC_LOW,T_P_MBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v/>
-      </c>
-      <c r="D120" t="n">
-        <v/>
-      </c>
-      <c r="E120" t="n">
-        <v/>
-      </c>
       <c r="F120" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G120" t="n">
-        <v/>
-      </c>
-      <c r="H120" t="n">
-        <v/>
-      </c>
-      <c r="I120" t="n">
-        <v/>
       </c>
     </row>
     <row r="121">
@@ -5041,9 +3650,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D121" t="n">
-        <v/>
-      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5071,36 +3677,15 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
-        <v/>
-      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>T_P_MBEVELC_MED,T_P_MBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v/>
-      </c>
-      <c r="D122" t="n">
-        <v/>
-      </c>
-      <c r="E122" t="n">
-        <v/>
-      </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G122" t="n">
-        <v/>
-      </c>
-      <c r="H122" t="n">
-        <v/>
-      </c>
-      <c r="I122" t="n">
-        <v/>
       </c>
     </row>
     <row r="123">
@@ -5119,9 +3704,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D123" t="n">
-        <v/>
-      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5149,36 +3731,15 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
-        <v/>
-      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>T_P_MBEVELC_LOW,T_P_MBEVELC_MED</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v/>
-      </c>
-      <c r="D124" t="n">
-        <v/>
-      </c>
-      <c r="E124" t="n">
-        <v/>
-      </c>
       <c r="F124" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G124" t="n">
-        <v/>
-      </c>
-      <c r="H124" t="n">
-        <v/>
-      </c>
-      <c r="I124" t="n">
-        <v/>
       </c>
     </row>
     <row r="125">
@@ -5197,9 +3758,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D125" t="n">
-        <v/>
-      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5227,36 +3785,15 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
-        <v/>
-      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>T_P_BICEPET_LOW,T_P_BICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v/>
-      </c>
-      <c r="D126" t="n">
-        <v/>
-      </c>
-      <c r="E126" t="n">
-        <v/>
-      </c>
       <c r="F126" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G126" t="n">
-        <v/>
-      </c>
-      <c r="H126" t="n">
-        <v/>
-      </c>
-      <c r="I126" t="n">
-        <v/>
       </c>
     </row>
     <row r="127">
@@ -5275,9 +3812,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D127" t="n">
-        <v/>
-      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5305,36 +3839,15 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
-        <v/>
-      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>T_P_BICEPET_MED,T_P_BICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C128" t="n">
-        <v/>
-      </c>
-      <c r="D128" t="n">
-        <v/>
-      </c>
-      <c r="E128" t="n">
-        <v/>
-      </c>
       <c r="F128" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G128" t="n">
-        <v/>
-      </c>
-      <c r="H128" t="n">
-        <v/>
-      </c>
-      <c r="I128" t="n">
-        <v/>
       </c>
     </row>
     <row r="129">
@@ -5353,9 +3866,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D129" t="n">
-        <v/>
-      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5383,36 +3893,15 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
-        <v/>
-      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>T_P_BICEPET_LOW,T_P_BICEPET_MED</t>
         </is>
       </c>
-      <c r="C130" t="n">
-        <v/>
-      </c>
-      <c r="D130" t="n">
-        <v/>
-      </c>
-      <c r="E130" t="n">
-        <v/>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G130" t="n">
-        <v/>
-      </c>
-      <c r="H130" t="n">
-        <v/>
-      </c>
-      <c r="I130" t="n">
-        <v/>
       </c>
     </row>
     <row r="131">
@@ -5431,9 +3920,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v/>
-      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5461,36 +3947,15 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
-        <v/>
-      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>T_P_BICEDSL_LOW,T_P_BICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v/>
-      </c>
-      <c r="D132" t="n">
-        <v/>
-      </c>
-      <c r="E132" t="n">
-        <v/>
-      </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G132" t="n">
-        <v/>
-      </c>
-      <c r="H132" t="n">
-        <v/>
-      </c>
-      <c r="I132" t="n">
-        <v/>
       </c>
     </row>
     <row r="133">
@@ -5509,9 +3974,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D133" t="n">
-        <v/>
-      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5539,36 +4001,15 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
-        <v/>
-      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>T_P_BICEDSL_MED,T_P_BICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C134" t="n">
-        <v/>
-      </c>
-      <c r="D134" t="n">
-        <v/>
-      </c>
-      <c r="E134" t="n">
-        <v/>
-      </c>
       <c r="F134" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G134" t="n">
-        <v/>
-      </c>
-      <c r="H134" t="n">
-        <v/>
-      </c>
-      <c r="I134" t="n">
-        <v/>
       </c>
     </row>
     <row r="135">
@@ -5587,9 +4028,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D135" t="n">
-        <v/>
-      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5617,36 +4055,15 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
-        <v/>
-      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>T_P_BICEDSL_LOW,T_P_BICEDSL_MED</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v/>
-      </c>
-      <c r="D136" t="n">
-        <v/>
-      </c>
-      <c r="E136" t="n">
-        <v/>
-      </c>
       <c r="F136" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G136" t="n">
-        <v/>
-      </c>
-      <c r="H136" t="n">
-        <v/>
-      </c>
-      <c r="I136" t="n">
-        <v/>
       </c>
     </row>
     <row r="137">
@@ -5665,9 +4082,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D137" t="n">
-        <v/>
-      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5695,36 +4109,15 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
-        <v/>
-      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>T_P_BBEVELC_LOW,T_P_BBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C138" t="n">
-        <v/>
-      </c>
-      <c r="D138" t="n">
-        <v/>
-      </c>
-      <c r="E138" t="n">
-        <v/>
-      </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G138" t="n">
-        <v/>
-      </c>
-      <c r="H138" t="n">
-        <v/>
-      </c>
-      <c r="I138" t="n">
-        <v/>
       </c>
     </row>
     <row r="139">
@@ -5743,9 +4136,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D139" t="n">
-        <v/>
-      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5773,36 +4163,15 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
-        <v/>
-      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>T_P_BBEVELC_MED,T_P_BBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v/>
-      </c>
-      <c r="D140" t="n">
-        <v/>
-      </c>
-      <c r="E140" t="n">
-        <v/>
-      </c>
       <c r="F140" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G140" t="n">
-        <v/>
-      </c>
-      <c r="H140" t="n">
-        <v/>
-      </c>
-      <c r="I140" t="n">
-        <v/>
       </c>
     </row>
     <row r="141">
@@ -5821,9 +4190,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D141" t="n">
-        <v/>
-      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5851,36 +4217,15 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
-        <v/>
-      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>T_P_BBEVELC_LOW,T_P_BBEVELC_MED</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v/>
-      </c>
-      <c r="D142" t="n">
-        <v/>
-      </c>
-      <c r="E142" t="n">
-        <v/>
-      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G142" t="n">
-        <v/>
-      </c>
-      <c r="H142" t="n">
-        <v/>
-      </c>
-      <c r="I142" t="n">
-        <v/>
       </c>
     </row>
     <row r="143">
@@ -5899,9 +4244,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D143" t="n">
-        <v/>
-      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>LO</t>
@@ -5929,36 +4271,15 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="n">
-        <v/>
-      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>T_P_BICELPG_LOW,T_P_BICELPG_HIGH</t>
         </is>
       </c>
-      <c r="C144" t="n">
-        <v/>
-      </c>
-      <c r="D144" t="n">
-        <v/>
-      </c>
-      <c r="E144" t="n">
-        <v/>
-      </c>
       <c r="F144" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G144" t="n">
-        <v/>
-      </c>
-      <c r="H144" t="n">
-        <v/>
-      </c>
-      <c r="I144" t="n">
-        <v/>
       </c>
     </row>
     <row r="145">
@@ -5977,9 +4298,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D145" t="n">
-        <v/>
-      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6007,36 +4325,15 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="n">
-        <v/>
-      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>T_P_BICELPG_MED,T_P_BICELPG_HIGH</t>
         </is>
       </c>
-      <c r="C146" t="n">
-        <v/>
-      </c>
-      <c r="D146" t="n">
-        <v/>
-      </c>
-      <c r="E146" t="n">
-        <v/>
-      </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G146" t="n">
-        <v/>
-      </c>
-      <c r="H146" t="n">
-        <v/>
-      </c>
-      <c r="I146" t="n">
-        <v/>
       </c>
     </row>
     <row r="147">
@@ -6055,9 +4352,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D147" t="n">
-        <v/>
-      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6085,36 +4379,15 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
-        <v/>
-      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>T_P_BICELPG_LOW,T_P_BICELPG_MED</t>
         </is>
       </c>
-      <c r="C148" t="n">
-        <v/>
-      </c>
-      <c r="D148" t="n">
-        <v/>
-      </c>
-      <c r="E148" t="n">
-        <v/>
-      </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G148" t="n">
-        <v/>
-      </c>
-      <c r="H148" t="n">
-        <v/>
-      </c>
-      <c r="I148" t="n">
-        <v/>
       </c>
     </row>
     <row r="149">
@@ -6133,9 +4406,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v/>
-      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6163,36 +4433,15 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
-        <v/>
-      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>T_P_BFCH2R_LOW,T_P_BFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C150" t="n">
-        <v/>
-      </c>
-      <c r="D150" t="n">
-        <v/>
-      </c>
-      <c r="E150" t="n">
-        <v/>
-      </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G150" t="n">
-        <v/>
-      </c>
-      <c r="H150" t="n">
-        <v/>
-      </c>
-      <c r="I150" t="n">
-        <v/>
       </c>
     </row>
     <row r="151">
@@ -6211,9 +4460,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D151" t="n">
-        <v/>
-      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6241,36 +4487,15 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
-        <v/>
-      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>T_P_BFCH2R_MED,T_P_BFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C152" t="n">
-        <v/>
-      </c>
-      <c r="D152" t="n">
-        <v/>
-      </c>
-      <c r="E152" t="n">
-        <v/>
-      </c>
       <c r="F152" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G152" t="n">
-        <v/>
-      </c>
-      <c r="H152" t="n">
-        <v/>
-      </c>
-      <c r="I152" t="n">
-        <v/>
       </c>
     </row>
     <row r="153">
@@ -6289,9 +4514,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D153" t="n">
-        <v/>
-      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6319,36 +4541,15 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
-        <v/>
-      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>T_P_BFCH2R_LOW,T_P_BFCH2R_MED</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v/>
-      </c>
-      <c r="D154" t="n">
-        <v/>
-      </c>
-      <c r="E154" t="n">
-        <v/>
-      </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G154" t="n">
-        <v/>
-      </c>
-      <c r="H154" t="n">
-        <v/>
-      </c>
-      <c r="I154" t="n">
-        <v/>
       </c>
     </row>
     <row r="155">
@@ -6367,9 +4568,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D155" t="n">
-        <v/>
-      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6397,36 +4595,15 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
-        <v/>
-      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>T_F_LTICEPET_LOW,T_F_LTICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C156" t="n">
-        <v/>
-      </c>
-      <c r="D156" t="n">
-        <v/>
-      </c>
-      <c r="E156" t="n">
-        <v/>
-      </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G156" t="n">
-        <v/>
-      </c>
-      <c r="H156" t="n">
-        <v/>
-      </c>
-      <c r="I156" t="n">
-        <v/>
       </c>
     </row>
     <row r="157">
@@ -6445,9 +4622,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D157" t="n">
-        <v/>
-      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6475,36 +4649,15 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
-        <v/>
-      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>T_F_LTICEPET_MED,T_F_LTICEPET_HIGH</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v/>
-      </c>
-      <c r="D158" t="n">
-        <v/>
-      </c>
-      <c r="E158" t="n">
-        <v/>
-      </c>
       <c r="F158" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G158" t="n">
-        <v/>
-      </c>
-      <c r="H158" t="n">
-        <v/>
-      </c>
-      <c r="I158" t="n">
-        <v/>
       </c>
     </row>
     <row r="159">
@@ -6523,9 +4676,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D159" t="n">
-        <v/>
-      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6553,36 +4703,15 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
-        <v/>
-      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>T_F_LTICEPET_LOW,T_F_LTICEPET_MED</t>
         </is>
       </c>
-      <c r="C160" t="n">
-        <v/>
-      </c>
-      <c r="D160" t="n">
-        <v/>
-      </c>
-      <c r="E160" t="n">
-        <v/>
-      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G160" t="n">
-        <v/>
-      </c>
-      <c r="H160" t="n">
-        <v/>
-      </c>
-      <c r="I160" t="n">
-        <v/>
       </c>
     </row>
     <row r="161">
@@ -6601,9 +4730,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D161" t="n">
-        <v/>
-      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6631,36 +4757,15 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
-        <v/>
-      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>T_F_LTICEDSL_LOW,T_F_LTICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C162" t="n">
-        <v/>
-      </c>
-      <c r="D162" t="n">
-        <v/>
-      </c>
-      <c r="E162" t="n">
-        <v/>
-      </c>
       <c r="F162" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G162" t="n">
-        <v/>
-      </c>
-      <c r="H162" t="n">
-        <v/>
-      </c>
-      <c r="I162" t="n">
-        <v/>
       </c>
     </row>
     <row r="163">
@@ -6679,9 +4784,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D163" t="n">
-        <v/>
-      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6709,36 +4811,15 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
-        <v/>
-      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>T_F_LTICEDSL_MED,T_F_LTICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C164" t="n">
-        <v/>
-      </c>
-      <c r="D164" t="n">
-        <v/>
-      </c>
-      <c r="E164" t="n">
-        <v/>
-      </c>
       <c r="F164" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G164" t="n">
-        <v/>
-      </c>
-      <c r="H164" t="n">
-        <v/>
-      </c>
-      <c r="I164" t="n">
-        <v/>
       </c>
     </row>
     <row r="165">
@@ -6757,9 +4838,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D165" t="n">
-        <v/>
-      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6787,36 +4865,15 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
-        <v/>
-      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>T_F_LTICEDSL_LOW,T_F_LTICEDSL_MED</t>
         </is>
       </c>
-      <c r="C166" t="n">
-        <v/>
-      </c>
-      <c r="D166" t="n">
-        <v/>
-      </c>
-      <c r="E166" t="n">
-        <v/>
-      </c>
       <c r="F166" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G166" t="n">
-        <v/>
-      </c>
-      <c r="H166" t="n">
-        <v/>
-      </c>
-      <c r="I166" t="n">
-        <v/>
       </c>
     </row>
     <row r="167">
@@ -6835,9 +4892,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D167" t="n">
-        <v/>
-      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6865,36 +4919,15 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
-        <v/>
-      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>T_F_LTBEVELC_LOW,T_F_LTBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C168" t="n">
-        <v/>
-      </c>
-      <c r="D168" t="n">
-        <v/>
-      </c>
-      <c r="E168" t="n">
-        <v/>
-      </c>
       <c r="F168" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G168" t="n">
-        <v/>
-      </c>
-      <c r="H168" t="n">
-        <v/>
-      </c>
-      <c r="I168" t="n">
-        <v/>
       </c>
     </row>
     <row r="169">
@@ -6913,9 +4946,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D169" t="n">
-        <v/>
-      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>LO</t>
@@ -6943,36 +4973,15 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
-        <v/>
-      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>T_F_LTBEVELC_MED,T_F_LTBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C170" t="n">
-        <v/>
-      </c>
-      <c r="D170" t="n">
-        <v/>
-      </c>
-      <c r="E170" t="n">
-        <v/>
-      </c>
       <c r="F170" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G170" t="n">
-        <v/>
-      </c>
-      <c r="H170" t="n">
-        <v/>
-      </c>
-      <c r="I170" t="n">
-        <v/>
       </c>
     </row>
     <row r="171">
@@ -6991,9 +5000,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D171" t="n">
-        <v/>
-      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7021,36 +5027,15 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
-        <v/>
-      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>T_F_LTBEVELC_LOW,T_F_LTBEVELC_MED</t>
         </is>
       </c>
-      <c r="C172" t="n">
-        <v/>
-      </c>
-      <c r="D172" t="n">
-        <v/>
-      </c>
-      <c r="E172" t="n">
-        <v/>
-      </c>
       <c r="F172" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G172" t="n">
-        <v/>
-      </c>
-      <c r="H172" t="n">
-        <v/>
-      </c>
-      <c r="I172" t="n">
-        <v/>
       </c>
     </row>
     <row r="173">
@@ -7069,9 +5054,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D173" t="n">
-        <v/>
-      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7099,36 +5081,15 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="n">
-        <v/>
-      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>T_F_LTFCH2R_LOW,T_F_LTFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C174" t="n">
-        <v/>
-      </c>
-      <c r="D174" t="n">
-        <v/>
-      </c>
-      <c r="E174" t="n">
-        <v/>
-      </c>
       <c r="F174" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G174" t="n">
-        <v/>
-      </c>
-      <c r="H174" t="n">
-        <v/>
-      </c>
-      <c r="I174" t="n">
-        <v/>
       </c>
     </row>
     <row r="175">
@@ -7147,9 +5108,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D175" t="n">
-        <v/>
-      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7177,36 +5135,15 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="n">
-        <v/>
-      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>T_F_LTFCH2R_MED,T_F_LTFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C176" t="n">
-        <v/>
-      </c>
-      <c r="D176" t="n">
-        <v/>
-      </c>
-      <c r="E176" t="n">
-        <v/>
-      </c>
       <c r="F176" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G176" t="n">
-        <v/>
-      </c>
-      <c r="H176" t="n">
-        <v/>
-      </c>
-      <c r="I176" t="n">
-        <v/>
       </c>
     </row>
     <row r="177">
@@ -7225,9 +5162,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D177" t="n">
-        <v/>
-      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7255,36 +5189,15 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="n">
-        <v/>
-      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>T_F_LTFCH2R_LOW,T_F_LTFCH2R_MED</t>
         </is>
       </c>
-      <c r="C178" t="n">
-        <v/>
-      </c>
-      <c r="D178" t="n">
-        <v/>
-      </c>
-      <c r="E178" t="n">
-        <v/>
-      </c>
       <c r="F178" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G178" t="n">
-        <v/>
-      </c>
-      <c r="H178" t="n">
-        <v/>
-      </c>
-      <c r="I178" t="n">
-        <v/>
       </c>
     </row>
     <row r="179">
@@ -7303,9 +5216,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D179" t="n">
-        <v/>
-      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7333,36 +5243,15 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
-        <v/>
-      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>T_F_MTICEDSL_LOW,T_F_MTICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C180" t="n">
-        <v/>
-      </c>
-      <c r="D180" t="n">
-        <v/>
-      </c>
-      <c r="E180" t="n">
-        <v/>
-      </c>
       <c r="F180" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G180" t="n">
-        <v/>
-      </c>
-      <c r="H180" t="n">
-        <v/>
-      </c>
-      <c r="I180" t="n">
-        <v/>
       </c>
     </row>
     <row r="181">
@@ -7381,9 +5270,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D181" t="n">
-        <v/>
-      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7411,36 +5297,15 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="n">
-        <v/>
-      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>T_F_MTICEDSL_MED,T_F_MTICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C182" t="n">
-        <v/>
-      </c>
-      <c r="D182" t="n">
-        <v/>
-      </c>
-      <c r="E182" t="n">
-        <v/>
-      </c>
       <c r="F182" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G182" t="n">
-        <v/>
-      </c>
-      <c r="H182" t="n">
-        <v/>
-      </c>
-      <c r="I182" t="n">
-        <v/>
       </c>
     </row>
     <row r="183">
@@ -7459,9 +5324,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D183" t="n">
-        <v/>
-      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7489,36 +5351,15 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
-        <v/>
-      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>T_F_MTICEDSL_LOW,T_F_MTICEDSL_MED</t>
         </is>
       </c>
-      <c r="C184" t="n">
-        <v/>
-      </c>
-      <c r="D184" t="n">
-        <v/>
-      </c>
-      <c r="E184" t="n">
-        <v/>
-      </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G184" t="n">
-        <v/>
-      </c>
-      <c r="H184" t="n">
-        <v/>
-      </c>
-      <c r="I184" t="n">
-        <v/>
       </c>
     </row>
     <row r="185">
@@ -7537,9 +5378,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D185" t="n">
-        <v/>
-      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7567,36 +5405,15 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="n">
-        <v/>
-      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>T_F_MTBEVELC_LOW,T_F_MTBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C186" t="n">
-        <v/>
-      </c>
-      <c r="D186" t="n">
-        <v/>
-      </c>
-      <c r="E186" t="n">
-        <v/>
-      </c>
       <c r="F186" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G186" t="n">
-        <v/>
-      </c>
-      <c r="H186" t="n">
-        <v/>
-      </c>
-      <c r="I186" t="n">
-        <v/>
       </c>
     </row>
     <row r="187">
@@ -7615,9 +5432,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D187" t="n">
-        <v/>
-      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7645,36 +5459,15 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="n">
-        <v/>
-      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>T_F_MTBEVELC_MED,T_F_MTBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C188" t="n">
-        <v/>
-      </c>
-      <c r="D188" t="n">
-        <v/>
-      </c>
-      <c r="E188" t="n">
-        <v/>
-      </c>
       <c r="F188" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G188" t="n">
-        <v/>
-      </c>
-      <c r="H188" t="n">
-        <v/>
-      </c>
-      <c r="I188" t="n">
-        <v/>
       </c>
     </row>
     <row r="189">
@@ -7693,9 +5486,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D189" t="n">
-        <v/>
-      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7723,36 +5513,15 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="n">
-        <v/>
-      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>T_F_MTBEVELC_LOW,T_F_MTBEVELC_MED</t>
         </is>
       </c>
-      <c r="C190" t="n">
-        <v/>
-      </c>
-      <c r="D190" t="n">
-        <v/>
-      </c>
-      <c r="E190" t="n">
-        <v/>
-      </c>
       <c r="F190" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G190" t="n">
-        <v/>
-      </c>
-      <c r="H190" t="n">
-        <v/>
-      </c>
-      <c r="I190" t="n">
-        <v/>
       </c>
     </row>
     <row r="191">
@@ -7771,9 +5540,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D191" t="n">
-        <v/>
-      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7801,36 +5567,15 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="n">
-        <v/>
-      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>T_F_MTFCH2R_LOW,T_F_MTFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C192" t="n">
-        <v/>
-      </c>
-      <c r="D192" t="n">
-        <v/>
-      </c>
-      <c r="E192" t="n">
-        <v/>
-      </c>
       <c r="F192" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G192" t="n">
-        <v/>
-      </c>
-      <c r="H192" t="n">
-        <v/>
-      </c>
-      <c r="I192" t="n">
-        <v/>
       </c>
     </row>
     <row r="193">
@@ -7849,9 +5594,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D193" t="n">
-        <v/>
-      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7879,36 +5621,15 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
-        <v/>
-      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>T_F_MTFCH2R_MED,T_F_MTFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C194" t="n">
-        <v/>
-      </c>
-      <c r="D194" t="n">
-        <v/>
-      </c>
-      <c r="E194" t="n">
-        <v/>
-      </c>
       <c r="F194" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G194" t="n">
-        <v/>
-      </c>
-      <c r="H194" t="n">
-        <v/>
-      </c>
-      <c r="I194" t="n">
-        <v/>
       </c>
     </row>
     <row r="195">
@@ -7927,9 +5648,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D195" t="n">
-        <v/>
-      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>LO</t>
@@ -7957,36 +5675,15 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="n">
-        <v/>
-      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>T_F_MTFCH2R_LOW,T_F_MTFCH2R_MED</t>
         </is>
       </c>
-      <c r="C196" t="n">
-        <v/>
-      </c>
-      <c r="D196" t="n">
-        <v/>
-      </c>
-      <c r="E196" t="n">
-        <v/>
-      </c>
       <c r="F196" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G196" t="n">
-        <v/>
-      </c>
-      <c r="H196" t="n">
-        <v/>
-      </c>
-      <c r="I196" t="n">
-        <v/>
       </c>
     </row>
     <row r="197">
@@ -8005,9 +5702,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D197" t="n">
-        <v/>
-      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>LO</t>
@@ -8035,36 +5729,15 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="n">
-        <v/>
-      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>T_F_HTICEDSL_LOW,T_F_HTICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C198" t="n">
-        <v/>
-      </c>
-      <c r="D198" t="n">
-        <v/>
-      </c>
-      <c r="E198" t="n">
-        <v/>
-      </c>
       <c r="F198" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G198" t="n">
-        <v/>
-      </c>
-      <c r="H198" t="n">
-        <v/>
-      </c>
-      <c r="I198" t="n">
-        <v/>
       </c>
     </row>
     <row r="199">
@@ -8083,9 +5756,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D199" t="n">
-        <v/>
-      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>LO</t>
@@ -8113,36 +5783,15 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="n">
-        <v/>
-      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>T_F_HTICEDSL_MED,T_F_HTICEDSL_HIGH</t>
         </is>
       </c>
-      <c r="C200" t="n">
-        <v/>
-      </c>
-      <c r="D200" t="n">
-        <v/>
-      </c>
-      <c r="E200" t="n">
-        <v/>
-      </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G200" t="n">
-        <v/>
-      </c>
-      <c r="H200" t="n">
-        <v/>
-      </c>
-      <c r="I200" t="n">
-        <v/>
       </c>
     </row>
     <row r="201">
@@ -8161,9 +5810,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D201" t="n">
-        <v/>
-      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>LO</t>
@@ -8191,36 +5837,15 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
-        <v/>
-      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>T_F_HTICEDSL_LOW,T_F_HTICEDSL_MED</t>
         </is>
       </c>
-      <c r="C202" t="n">
-        <v/>
-      </c>
-      <c r="D202" t="n">
-        <v/>
-      </c>
-      <c r="E202" t="n">
-        <v/>
-      </c>
       <c r="F202" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G202" t="n">
-        <v/>
-      </c>
-      <c r="H202" t="n">
-        <v/>
-      </c>
-      <c r="I202" t="n">
-        <v/>
       </c>
     </row>
     <row r="203">
@@ -8239,9 +5864,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D203" t="n">
-        <v/>
-      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>LO</t>
@@ -8269,36 +5891,15 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="n">
-        <v/>
-      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>T_F_HTBEVELC_LOW,T_F_HTBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C204" t="n">
-        <v/>
-      </c>
-      <c r="D204" t="n">
-        <v/>
-      </c>
-      <c r="E204" t="n">
-        <v/>
-      </c>
       <c r="F204" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G204" t="n">
-        <v/>
-      </c>
-      <c r="H204" t="n">
-        <v/>
-      </c>
-      <c r="I204" t="n">
-        <v/>
       </c>
     </row>
     <row r="205">
@@ -8317,9 +5918,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D205" t="n">
-        <v/>
-      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>LO</t>
@@ -8347,36 +5945,15 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
-        <v/>
-      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>T_F_HTBEVELC_MED,T_F_HTBEVELC_HIGH</t>
         </is>
       </c>
-      <c r="C206" t="n">
-        <v/>
-      </c>
-      <c r="D206" t="n">
-        <v/>
-      </c>
-      <c r="E206" t="n">
-        <v/>
-      </c>
       <c r="F206" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G206" t="n">
-        <v/>
-      </c>
-      <c r="H206" t="n">
-        <v/>
-      </c>
-      <c r="I206" t="n">
-        <v/>
       </c>
     </row>
     <row r="207">
@@ -8395,9 +5972,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D207" t="n">
-        <v/>
-      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>LO</t>
@@ -8425,36 +5999,15 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="n">
-        <v/>
-      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>T_F_HTBEVELC_LOW,T_F_HTBEVELC_MED</t>
         </is>
       </c>
-      <c r="C208" t="n">
-        <v/>
-      </c>
-      <c r="D208" t="n">
-        <v/>
-      </c>
-      <c r="E208" t="n">
-        <v/>
-      </c>
       <c r="F208" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G208" t="n">
-        <v/>
-      </c>
-      <c r="H208" t="n">
-        <v/>
-      </c>
-      <c r="I208" t="n">
-        <v/>
       </c>
     </row>
     <row r="209">
@@ -8473,9 +6026,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D209" t="n">
-        <v/>
-      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>LO</t>
@@ -8503,36 +6053,15 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
-        <v/>
-      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>T_F_HTFCH2R_LOW,T_F_HTFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C210" t="n">
-        <v/>
-      </c>
-      <c r="D210" t="n">
-        <v/>
-      </c>
-      <c r="E210" t="n">
-        <v/>
-      </c>
       <c r="F210" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G210" t="n">
-        <v/>
-      </c>
-      <c r="H210" t="n">
-        <v/>
-      </c>
-      <c r="I210" t="n">
-        <v/>
       </c>
     </row>
     <row r="211">
@@ -8551,9 +6080,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D211" t="n">
-        <v/>
-      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>LO</t>
@@ -8581,36 +6107,15 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
-        <v/>
-      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>T_F_HTFCH2R_MED,T_F_HTFCH2R_HIGH</t>
         </is>
       </c>
-      <c r="C212" t="n">
-        <v/>
-      </c>
-      <c r="D212" t="n">
-        <v/>
-      </c>
-      <c r="E212" t="n">
-        <v/>
-      </c>
       <c r="F212" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
-      </c>
-      <c r="G212" t="n">
-        <v/>
-      </c>
-      <c r="H212" t="n">
-        <v/>
-      </c>
-      <c r="I212" t="n">
-        <v/>
       </c>
     </row>
     <row r="213">
@@ -8629,9 +6134,6 @@
           <t>CAP,SYNC</t>
         </is>
       </c>
-      <c r="D213" t="n">
-        <v/>
-      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>LO</t>
@@ -8659,36 +6161,203 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
-        <v/>
-      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>T_F_HTFCH2R_LOW,T_F_HTFCH2R_MED</t>
         </is>
       </c>
-      <c r="C214" t="n">
-        <v/>
-      </c>
-      <c r="D214" t="n">
-        <v/>
-      </c>
-      <c r="E214" t="n">
-        <v/>
-      </c>
       <c r="F214" t="inlineStr">
         <is>
           <t>-0.3333</t>
         </is>
       </c>
-      <c r="G214" t="n">
-        <v/>
-      </c>
-      <c r="H214" t="n">
-        <v/>
-      </c>
-      <c r="I214" t="n">
-        <v/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GasNetworkBlendingConstraints</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ensures the input share of gas/biomethanol matches the output share of the gas network </t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>~TFM_INS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pset_CO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pset_CI</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Other_Indexes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cset_CN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FLO_EFF</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NGADD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NGADD</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FLO_EFF</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIMDD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BIM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BIM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BIMDD</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FLO_EFF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NGADD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BIM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BIM</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NGADD</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FLO_EFF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BIMDD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BIMDD</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
